--- a/artfynd/A 24596-2026 artfynd.xlsx
+++ b/artfynd/A 24596-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110927105</v>
+        <v>110927102</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelsågberget sydöst, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576398</v>
+        <v>576385</v>
       </c>
       <c r="R2" t="n">
-        <v>6757310</v>
+        <v>6757375</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110927102</v>
+        <v>110927101</v>
       </c>
       <c r="B3" t="n">
-        <v>77550</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576384.8514214228</v>
+        <v>576240</v>
       </c>
       <c r="R3" t="n">
-        <v>6757374.79138744</v>
+        <v>6757379</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +850,9 @@
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110927101</v>
+        <v>110927104</v>
       </c>
       <c r="B4" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelsågberget sydöst, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576240.1529091237</v>
+        <v>576372</v>
       </c>
       <c r="R4" t="n">
-        <v>6757379.458646191</v>
+        <v>6757341</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,19 +962,9 @@
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1028,6 +998,118 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110927105</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gammelsågberget sydöst, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576398</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6757310</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Kopparfors skogar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
